--- a/research/traditional_assets/database/data/oman/oman_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_investments_asset_management.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.203</v>
-      </c>
-      <c r="E2">
-        <v>0.0851</v>
+        <v>-0.371</v>
       </c>
       <c r="G2">
-        <v>0.3075079872204473</v>
+        <v>-19.2</v>
       </c>
       <c r="H2">
-        <v>0.3075079872204473</v>
+        <v>-19.2</v>
       </c>
       <c r="I2">
-        <v>0.8099041533546326</v>
+        <v>-96.89090909090909</v>
       </c>
       <c r="J2">
-        <v>0.7523407176616588</v>
+        <v>-96.89090909090909</v>
       </c>
       <c r="K2">
-        <v>1.649</v>
+        <v>-6.037</v>
       </c>
       <c r="L2">
-        <v>0.2634185303514377</v>
+        <v>-109.7636363636364</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04224207961007312</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0.3445419910551599</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04224207961007312</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0.3445419910551599</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>0.435</v>
+        <v>0.096</v>
       </c>
       <c r="V2">
-        <v>0.008331737215092895</v>
+        <v>0.001949634443541836</v>
       </c>
       <c r="W2">
-        <v>0.1026138064971752</v>
+        <v>-0.06948566253702206</v>
       </c>
       <c r="X2">
-        <v>0.09086749269802051</v>
+        <v>0.137988275959028</v>
       </c>
       <c r="Y2">
-        <v>0.01174631379915464</v>
+        <v>-0.20747393849605</v>
       </c>
       <c r="Z2">
-        <v>0.04702594690425036</v>
+        <v>0.0004157689836338209</v>
       </c>
       <c r="AA2">
-        <v>0.1222302242930756</v>
+        <v>-0.05242639497816409</v>
       </c>
       <c r="AB2">
-        <v>0.07491531541002516</v>
+        <v>0.1149997707263336</v>
       </c>
       <c r="AC2">
-        <v>0.04731490888305047</v>
+        <v>-0.1674261657044978</v>
       </c>
       <c r="AD2">
-        <v>44.7</v>
+        <v>47.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>44.7</v>
+        <v>47.2</v>
       </c>
       <c r="AG2">
-        <v>44.265</v>
+        <v>47.10400000000001</v>
       </c>
       <c r="AH2">
-        <v>0.4612527086987928</v>
+        <v>0.4894234757362091</v>
       </c>
       <c r="AI2">
-        <v>0.336926207884224</v>
+        <v>0.365778053316801</v>
       </c>
       <c r="AJ2">
-        <v>0.4588235294117647</v>
+        <v>0.4889147222452878</v>
       </c>
       <c r="AK2">
-        <v>0.3347449616213559</v>
+        <v>0.3653058692145428</v>
       </c>
       <c r="AL2">
-        <v>2.899</v>
+        <v>2.608</v>
       </c>
       <c r="AM2">
-        <v>2.899</v>
+        <v>2.608</v>
       </c>
       <c r="AN2">
-        <v>9.74918211559433</v>
+        <v>-8.91238670694864</v>
       </c>
       <c r="AO2">
-        <v>1.748878923766816</v>
+        <v>-2.043328220858896</v>
       </c>
       <c r="AP2">
-        <v>9.654307524536533</v>
+        <v>-8.894259818731118</v>
       </c>
       <c r="AQ2">
-        <v>1.748878923766816</v>
+        <v>-2.043328220858896</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Batinah Development and Investment Holding Co. SAOG (MSM:DBIH)</t>
+          <t>Al Anwar Investments SAOG (MSM:AAIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,119 +718,101 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.203</v>
-      </c>
-      <c r="E3">
-        <v>0.0851</v>
-      </c>
-      <c r="G3">
-        <v>-0.1783216783216783</v>
-      </c>
-      <c r="H3">
-        <v>-0.1783216783216783</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>0.8578512396694216</v>
-      </c>
       <c r="K3">
-        <v>1.05</v>
-      </c>
-      <c r="L3">
-        <v>0.7342657342657344</v>
+        <v>-5.57</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.08</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04541484716157206</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>-0.3734290843806104</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04541484716157206</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>-0.3734290843806104</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>-0.187</v>
+        <v>0.322</v>
       </c>
       <c r="V3">
-        <v>-0.04782608695652174</v>
+        <v>0.007030567685589521</v>
       </c>
       <c r="W3">
-        <v>0.1977401129943503</v>
+        <v>-0.06842751842751843</v>
       </c>
       <c r="X3">
-        <v>0.06947898729246095</v>
+        <v>0.1681995850349177</v>
       </c>
       <c r="Y3">
-        <v>0.1282611257018894</v>
+        <v>-0.2366271034624362</v>
       </c>
       <c r="Z3">
-        <v>0.2516719464977121</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.2158970912930787</v>
+        <v>-0.03889127974625033</v>
       </c>
       <c r="AB3">
-        <v>0.06947898729246095</v>
+        <v>0.1222225745695291</v>
       </c>
       <c r="AC3">
-        <v>0.1464181040006177</v>
+        <v>-0.1611138543157794</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="AG3">
-        <v>0.187</v>
+        <v>46.878</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.5075268817204301</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.3843648208469056</v>
       </c>
       <c r="AJ3">
-        <v>0.04564315352697095</v>
+        <v>0.5058158354733594</v>
       </c>
       <c r="AK3">
-        <v>0.0276750036998668</v>
+        <v>0.3827462891294763</v>
       </c>
       <c r="AL3">
-        <v>0.029</v>
+        <v>2.59</v>
       </c>
       <c r="AM3">
-        <v>0.029</v>
+        <v>2.59</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-9.691991786447639</v>
       </c>
       <c r="AO3">
-        <v>49.3103448275862</v>
+        <v>-1.884169884169884</v>
       </c>
       <c r="AP3">
-        <v>0.1978835978835979</v>
+        <v>-9.625872689938397</v>
       </c>
       <c r="AQ3">
-        <v>49.3103448275862</v>
+        <v>-1.884169884169884</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Anwar Investments SAOG (MSM:AAIC)</t>
+          <t>Al Batinah Development and Investment Holding Co. SAOG (MSM:DBIH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,23 +831,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.371</v>
+      </c>
       <c r="G4">
-        <v>0.4513457556935818</v>
+        <v>2.981818181818182</v>
       </c>
       <c r="H4">
-        <v>0.4513457556935818</v>
+        <v>2.981818181818182</v>
       </c>
       <c r="I4">
-        <v>0.7536231884057971</v>
+        <v>-8.163636363636364</v>
       </c>
       <c r="J4">
-        <v>0.7536231884057971</v>
+        <v>-8.163636363636364</v>
       </c>
       <c r="K4">
-        <v>0.599</v>
+        <v>-0.467</v>
       </c>
       <c r="L4">
-        <v>0.1240165631469979</v>
+        <v>-8.490909090909092</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,7 +859,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,79 +868,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>-0.226</v>
+      </c>
+      <c r="V4">
+        <v>-0.06569767441860465</v>
+      </c>
+      <c r="W4">
+        <v>-0.07054380664652568</v>
+      </c>
+      <c r="X4">
+        <v>0.1077769668831382</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1783207735296639</v>
+      </c>
+      <c r="Z4">
+        <v>0.008079917731746732</v>
+      </c>
+      <c r="AA4">
+        <v>-0.06596151021007786</v>
+      </c>
+      <c r="AB4">
+        <v>0.1077769668831382</v>
+      </c>
+      <c r="AC4">
+        <v>-0.173738477093216</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0.226</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0.06164757228587016</v>
+      </c>
+      <c r="AK4">
+        <v>0.03495205691308383</v>
+      </c>
+      <c r="AL4">
+        <v>0.018</v>
+      </c>
+      <c r="AM4">
+        <v>0.018</v>
+      </c>
+      <c r="AN4">
         <v>-0</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0.622</v>
-      </c>
-      <c r="V4">
-        <v>0.01287784679089027</v>
-      </c>
-      <c r="W4">
-        <v>0.007487499999999999</v>
-      </c>
-      <c r="X4">
-        <v>0.1122559981035801</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1047684981035801</v>
-      </c>
-      <c r="Z4">
-        <v>0.03790137794657711</v>
-      </c>
-      <c r="AA4">
-        <v>0.02856335729307261</v>
-      </c>
-      <c r="AB4">
-        <v>0.08035164352758939</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05178828623451678</v>
-      </c>
-      <c r="AD4">
-        <v>44.7</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>44.7</v>
-      </c>
-      <c r="AG4">
-        <v>44.078</v>
-      </c>
-      <c r="AH4">
-        <v>0.4806451612903226</v>
-      </c>
-      <c r="AI4">
-        <v>0.3544805709754164</v>
-      </c>
-      <c r="AJ4">
-        <v>0.4771482387581459</v>
-      </c>
-      <c r="AK4">
-        <v>0.3512807025932833</v>
-      </c>
-      <c r="AL4">
-        <v>2.87</v>
-      </c>
-      <c r="AM4">
-        <v>2.87</v>
-      </c>
-      <c r="AN4">
-        <v>12.28021978021978</v>
-      </c>
       <c r="AO4">
-        <v>1.268292682926829</v>
+        <v>-24.94444444444445</v>
       </c>
       <c r="AP4">
-        <v>12.10934065934066</v>
+        <v>-0.5305164319248826</v>
       </c>
       <c r="AQ4">
-        <v>1.268292682926829</v>
+        <v>-24.94444444444445</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/oman/oman_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_investments_asset_management.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.371</v>
+        <v>-0.2375</v>
+      </c>
+      <c r="E2">
+        <v>-0.188</v>
       </c>
       <c r="G2">
-        <v>-19.2</v>
+        <v>0.3594851706771124</v>
       </c>
       <c r="H2">
-        <v>-19.2</v>
+        <v>0.3594851706771124</v>
       </c>
       <c r="I2">
-        <v>-96.89090909090909</v>
+        <v>0.7903749300503636</v>
       </c>
       <c r="J2">
-        <v>-96.89090909090909</v>
+        <v>0.7903749300503636</v>
       </c>
       <c r="K2">
-        <v>-6.037</v>
+        <v>4.348000000000001</v>
       </c>
       <c r="L2">
-        <v>-109.7636363636364</v>
+        <v>0.4866256295467264</v>
       </c>
       <c r="M2">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="N2">
-        <v>0.04224207961007312</v>
+        <v>0.05409904286308781</v>
       </c>
       <c r="O2">
-        <v>-0.3445419910551599</v>
+        <v>0.5979760809567617</v>
       </c>
       <c r="P2">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>0.04224207961007312</v>
+        <v>0.05409904286308781</v>
       </c>
       <c r="R2">
-        <v>-0.3445419910551599</v>
+        <v>0.5979760809567617</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.096</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="V2">
-        <v>0.001949634443541836</v>
+        <v>0.0149812734082397</v>
       </c>
       <c r="W2">
-        <v>-0.06948566253702206</v>
+        <v>-0.01609245748454973</v>
       </c>
       <c r="X2">
-        <v>0.137988275959028</v>
+        <v>0.09870155768788627</v>
       </c>
       <c r="Y2">
-        <v>-0.20747393849605</v>
+        <v>-0.114794015172436</v>
       </c>
       <c r="Z2">
-        <v>0.0004157689836338209</v>
+        <v>0.06938512432633917</v>
       </c>
       <c r="AA2">
-        <v>-0.05242639497816409</v>
+        <v>-0.01772621073684825</v>
       </c>
       <c r="AB2">
-        <v>0.1149997707263336</v>
+        <v>0.08507362649128977</v>
       </c>
       <c r="AC2">
-        <v>-0.1674261657044978</v>
+        <v>-0.102799837228138</v>
       </c>
       <c r="AD2">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="AG2">
-        <v>47.10400000000001</v>
+        <v>39.88</v>
       </c>
       <c r="AH2">
-        <v>0.4894234757362091</v>
+        <v>0.457929167606587</v>
       </c>
       <c r="AI2">
-        <v>0.365778053316801</v>
+        <v>0.3086513608027976</v>
       </c>
       <c r="AJ2">
-        <v>0.4889147222452878</v>
+        <v>0.4534910166022288</v>
       </c>
       <c r="AK2">
-        <v>0.3653058692145428</v>
+        <v>0.3048463537685369</v>
       </c>
       <c r="AL2">
-        <v>2.608</v>
+        <v>2.674</v>
       </c>
       <c r="AM2">
-        <v>2.608</v>
+        <v>2.674</v>
       </c>
       <c r="AN2">
-        <v>-8.91238670694864</v>
+        <v>5.717504576820167</v>
       </c>
       <c r="AO2">
-        <v>-2.043328220858896</v>
+        <v>2.640987284966342</v>
       </c>
       <c r="AP2">
-        <v>-8.894259818731118</v>
+        <v>5.616110406984932</v>
       </c>
       <c r="AQ2">
-        <v>-2.043328220858896</v>
+        <v>2.640987284966342</v>
       </c>
     </row>
     <row r="3">
@@ -718,26 +721,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.129</v>
+      </c>
+      <c r="E3">
+        <v>-0.188</v>
+      </c>
+      <c r="G3">
+        <v>0.4125</v>
+      </c>
+      <c r="H3">
+        <v>0.4125</v>
+      </c>
+      <c r="I3">
+        <v>0.8727272727272726</v>
+      </c>
+      <c r="J3">
+        <v>0.8727272727272726</v>
+      </c>
       <c r="K3">
-        <v>-5.57</v>
+        <v>4.94</v>
+      </c>
+      <c r="L3">
+        <v>0.5613636363636364</v>
       </c>
       <c r="M3">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="N3">
-        <v>0.04541484716157206</v>
+        <v>0.06310679611650485</v>
       </c>
       <c r="O3">
-        <v>-0.3734290843806104</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="Q3">
-        <v>0.04541484716157206</v>
+        <v>0.06310679611650485</v>
       </c>
       <c r="R3">
-        <v>-0.3734290843806104</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -746,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.322</v>
+        <v>1.31</v>
       </c>
       <c r="V3">
-        <v>0.007030567685589521</v>
+        <v>0.03179611650485437</v>
       </c>
       <c r="W3">
-        <v>-0.06842751842751843</v>
+        <v>0.06534391534391536</v>
       </c>
       <c r="X3">
-        <v>0.1681995850349177</v>
+        <v>0.1163835588495401</v>
       </c>
       <c r="Y3">
-        <v>-0.2366271034624362</v>
+        <v>-0.05103964350562479</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.07184963830238901</v>
       </c>
       <c r="AA3">
-        <v>-0.03889127974625033</v>
+        <v>0.06270513888208494</v>
       </c>
       <c r="AB3">
-        <v>0.1222225745695291</v>
+        <v>0.08912769645634715</v>
       </c>
       <c r="AC3">
-        <v>-0.1611138543157794</v>
+        <v>-0.02642255757426221</v>
       </c>
       <c r="AD3">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="AG3">
-        <v>46.878</v>
+        <v>39.29</v>
       </c>
       <c r="AH3">
-        <v>0.5075268817204301</v>
+        <v>0.4963325183374083</v>
       </c>
       <c r="AI3">
-        <v>0.3843648208469056</v>
+        <v>0.3209486166007905</v>
       </c>
       <c r="AJ3">
-        <v>0.5058158354733594</v>
+        <v>0.4881351720710647</v>
       </c>
       <c r="AK3">
-        <v>0.3827462891294763</v>
+        <v>0.3138429587027718</v>
       </c>
       <c r="AL3">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="AM3">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="AN3">
-        <v>-9.691991786447639</v>
+        <v>5.286458333333334</v>
       </c>
       <c r="AO3">
-        <v>-1.884169884169884</v>
+        <v>2.909090909090909</v>
       </c>
       <c r="AP3">
-        <v>-9.625872689938397</v>
+        <v>5.115885416666667</v>
       </c>
       <c r="AQ3">
-        <v>-1.884169884169884</v>
+        <v>2.909090909090909</v>
       </c>
     </row>
     <row r="4">
@@ -832,25 +856,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.371</v>
+        <v>-0.346</v>
       </c>
       <c r="G4">
-        <v>2.981818181818182</v>
+        <v>-3.096296296296296</v>
       </c>
       <c r="H4">
-        <v>2.981818181818182</v>
+        <v>-3.096296296296296</v>
       </c>
       <c r="I4">
-        <v>-8.163636363636364</v>
+        <v>-4.577777777777778</v>
       </c>
       <c r="J4">
-        <v>-8.163636363636364</v>
+        <v>-4.577777777777778</v>
       </c>
       <c r="K4">
-        <v>-0.467</v>
+        <v>-0.592</v>
       </c>
       <c r="L4">
-        <v>-8.490909090909092</v>
+        <v>-4.385185185185184</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,31 +898,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>-0.226</v>
+        <v>-0.59</v>
       </c>
       <c r="V4">
-        <v>-0.06569767441860465</v>
+        <v>-0.08600583090379008</v>
       </c>
       <c r="W4">
-        <v>-0.07054380664652568</v>
+        <v>-0.09752883031301482</v>
       </c>
       <c r="X4">
-        <v>0.1077769668831382</v>
+        <v>0.08101955652623238</v>
       </c>
       <c r="Y4">
-        <v>-0.1783207735296639</v>
+        <v>-0.1785483868392472</v>
       </c>
       <c r="Z4">
-        <v>0.008079917731746732</v>
+        <v>0.02144218551461245</v>
       </c>
       <c r="AA4">
-        <v>-0.06596151021007786</v>
+        <v>-0.09815756035578144</v>
       </c>
       <c r="AB4">
-        <v>0.1077769668831382</v>
+        <v>0.08101955652623238</v>
       </c>
       <c r="AC4">
-        <v>-0.173738477093216</v>
+        <v>-0.1791771168820138</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -910,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.226</v>
+        <v>0.59</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -919,28 +943,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.06164757228587016</v>
+        <v>0.07919463087248321</v>
       </c>
       <c r="AK4">
-        <v>0.03495205691308383</v>
+        <v>0.1047957371225577</v>
       </c>
       <c r="AL4">
-        <v>0.018</v>
+        <v>0.034</v>
       </c>
       <c r="AM4">
-        <v>0.018</v>
+        <v>0.034</v>
       </c>
       <c r="AN4">
         <v>-0</v>
       </c>
       <c r="AO4">
-        <v>-24.94444444444445</v>
+        <v>-18.17647058823529</v>
       </c>
       <c r="AP4">
-        <v>-0.5305164319248826</v>
+        <v>-1.018998272884283</v>
       </c>
       <c r="AQ4">
-        <v>-24.94444444444445</v>
+        <v>-18.17647058823529</v>
       </c>
     </row>
   </sheetData>
